--- a/Data/FlightPlan/FPL_20OCT26.xlsx
+++ b/Data/FlightPlan/FPL_20OCT26.xlsx
@@ -776,51 +776,60 @@
     <t>14:30</t>
   </si>
   <si>
+    <t>15:20</t>
+  </si>
+  <si>
+    <t>16:15</t>
+  </si>
+  <si>
+    <t>22:00</t>
+  </si>
+  <si>
+    <t>VN-A580</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>10:55</t>
+  </si>
+  <si>
+    <t>10:47</t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>VN-A607</t>
+  </si>
+  <si>
+    <t>SIN</t>
+  </si>
+  <si>
+    <t>17:55</t>
+  </si>
+  <si>
+    <t>VN-A629</t>
+  </si>
+  <si>
+    <t>10:40</t>
+  </si>
+  <si>
+    <t>11:07</t>
+  </si>
+  <si>
+    <t>11:15</t>
+  </si>
+  <si>
+    <t>15:10</t>
+  </si>
+  <si>
+    <t>15:40</t>
+  </si>
+  <si>
     <t>17:15</t>
   </si>
   <si>
-    <t>VN-A580</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
-    <t>10:55</t>
-  </si>
-  <si>
-    <t>10:47</t>
-  </si>
-  <si>
-    <t>20:30</t>
-  </si>
-  <si>
-    <t>VN-A607</t>
-  </si>
-  <si>
-    <t>SIN</t>
-  </si>
-  <si>
-    <t>17:55</t>
-  </si>
-  <si>
-    <t>VN-A629</t>
-  </si>
-  <si>
-    <t>10:40</t>
-  </si>
-  <si>
-    <t>11:07</t>
-  </si>
-  <si>
-    <t>11:15</t>
-  </si>
-  <si>
-    <t>15:10</t>
-  </si>
-  <si>
-    <t>15:40</t>
-  </si>
-  <si>
     <t>19:25</t>
   </si>
   <si>
@@ -839,477 +848,474 @@
     <t>14:45</t>
   </si>
   <si>
+    <t>BMV</t>
+  </si>
+  <si>
+    <t>20:45</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
     <t>VII</t>
   </si>
   <si>
+    <t>06:35</t>
+  </si>
+  <si>
+    <t>07:20</t>
+  </si>
+  <si>
+    <t>08:42</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>10:38</t>
+  </si>
+  <si>
+    <t>12:40</t>
+  </si>
+  <si>
+    <t>20:55</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>06:30</t>
+  </si>
+  <si>
+    <t>DVO</t>
+  </si>
+  <si>
+    <t>23:45</t>
+  </si>
+  <si>
+    <t>VN-A634</t>
+  </si>
+  <si>
+    <t>05:45</t>
+  </si>
+  <si>
+    <t>08:05</t>
+  </si>
+  <si>
+    <t>10:14</t>
+  </si>
+  <si>
+    <t>21:25</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
+    <t>08:54</t>
+  </si>
+  <si>
+    <t>11:27</t>
+  </si>
+  <si>
+    <t>MFM</t>
+  </si>
+  <si>
+    <t>21:55</t>
+  </si>
+  <si>
+    <t>VN-A637</t>
+  </si>
+  <si>
+    <t>08:12</t>
+  </si>
+  <si>
+    <t>10:21</t>
+  </si>
+  <si>
+    <t>19:35</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>KUL</t>
+  </si>
+  <si>
+    <t>12:35</t>
+  </si>
+  <si>
+    <t>12:32</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
+    <t>08:25</t>
+  </si>
+  <si>
+    <t>09:42</t>
+  </si>
+  <si>
+    <t>10:05</t>
+  </si>
+  <si>
+    <t>11:22</t>
+  </si>
+  <si>
+    <t>12:05</t>
+  </si>
+  <si>
+    <t>PVG</t>
+  </si>
+  <si>
+    <t>02:15</t>
+  </si>
+  <si>
+    <t>05:25</t>
+  </si>
+  <si>
+    <t>VN-A642</t>
+  </si>
+  <si>
+    <t>07:55</t>
+  </si>
+  <si>
+    <t>09:19</t>
+  </si>
+  <si>
+    <t>09:45</t>
+  </si>
+  <si>
+    <t>11:02</t>
+  </si>
+  <si>
+    <t>12:46</t>
+  </si>
+  <si>
+    <t>VN-A644</t>
+  </si>
+  <si>
+    <t>FUK</t>
+  </si>
+  <si>
+    <t>11:45</t>
+  </si>
+  <si>
+    <t>12:39</t>
+  </si>
+  <si>
+    <t>RMQ</t>
+  </si>
+  <si>
+    <t>VN-A645</t>
+  </si>
+  <si>
+    <t>07:40</t>
+  </si>
+  <si>
+    <t>07:39</t>
+  </si>
+  <si>
+    <t>09:52</t>
+  </si>
+  <si>
+    <t>12:13</t>
+  </si>
+  <si>
+    <t>15:05</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>VN-A646</t>
+  </si>
+  <si>
+    <t>12:55</t>
+  </si>
+  <si>
+    <t>13:17</t>
+  </si>
+  <si>
+    <t>13:25</t>
+  </si>
+  <si>
+    <t>VN-A647</t>
+  </si>
+  <si>
+    <t>10:12</t>
+  </si>
+  <si>
+    <t>VN-A648</t>
+  </si>
+  <si>
+    <t>13:57</t>
+  </si>
+  <si>
+    <t>VN-A649</t>
+  </si>
+  <si>
+    <t>14:51</t>
+  </si>
+  <si>
+    <t>01:40</t>
+  </si>
+  <si>
+    <t>VN-A651</t>
+  </si>
+  <si>
+    <t>09:08</t>
+  </si>
+  <si>
+    <t>11:17</t>
+  </si>
+  <si>
+    <t>13:19</t>
+  </si>
+  <si>
+    <t>17:30</t>
+  </si>
+  <si>
+    <t>21:10</t>
+  </si>
+  <si>
+    <t>23:20</t>
+  </si>
+  <si>
+    <t>VN-A653</t>
+  </si>
+  <si>
+    <t>11:57</t>
+  </si>
+  <si>
+    <t>HND</t>
+  </si>
+  <si>
+    <t>02:00</t>
+  </si>
+  <si>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>VN-A656</t>
+  </si>
+  <si>
+    <t>VN-A657</t>
+  </si>
+  <si>
+    <t>22:25</t>
+  </si>
+  <si>
+    <t>VN-A658</t>
+  </si>
+  <si>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>07:29</t>
+  </si>
+  <si>
+    <t>11:50</t>
+  </si>
+  <si>
+    <t>11:38</t>
+  </si>
+  <si>
+    <t>ENH</t>
+  </si>
+  <si>
+    <t>21:15</t>
+  </si>
+  <si>
+    <t>01:15</t>
+  </si>
+  <si>
+    <t>02:20</t>
+  </si>
+  <si>
+    <t>04:50</t>
+  </si>
+  <si>
+    <t>VN-A661</t>
+  </si>
+  <si>
+    <t>12:38</t>
+  </si>
+  <si>
+    <t>13:45</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>21:45</t>
+  </si>
+  <si>
+    <t>02:30</t>
+  </si>
+  <si>
+    <t>04:10</t>
+  </si>
+  <si>
+    <t>VN-A663</t>
+  </si>
+  <si>
+    <t>FSZ</t>
+  </si>
+  <si>
+    <t>13:56</t>
+  </si>
+  <si>
+    <t>14:40</t>
+  </si>
+  <si>
+    <t>CMB</t>
+  </si>
+  <si>
+    <t>21:50</t>
+  </si>
+  <si>
+    <t>VN-A667</t>
+  </si>
+  <si>
+    <t>13:29</t>
+  </si>
+  <si>
+    <t>VN-A668</t>
+  </si>
+  <si>
+    <t>09:44</t>
+  </si>
+  <si>
+    <t>12:09</t>
+  </si>
+  <si>
+    <t>VCL</t>
+  </si>
+  <si>
+    <t>23:30</t>
+  </si>
+  <si>
+    <t>VN-A669</t>
+  </si>
+  <si>
+    <t>HIJ</t>
+  </si>
+  <si>
+    <t>16:14</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>03:55</t>
+  </si>
+  <si>
+    <t>VN-A670</t>
+  </si>
+  <si>
+    <t>05:50</t>
+  </si>
+  <si>
+    <t>07:21</t>
+  </si>
+  <si>
+    <t>11:26</t>
+  </si>
+  <si>
+    <t>MNL</t>
+  </si>
+  <si>
+    <t>02:40</t>
+  </si>
+  <si>
+    <t>03:35</t>
+  </si>
+  <si>
+    <t>04:55</t>
+  </si>
+  <si>
+    <t>VN-A675</t>
+  </si>
+  <si>
+    <t>11:06</t>
+  </si>
+  <si>
+    <t>21:40</t>
+  </si>
+  <si>
+    <t>VN-A676</t>
+  </si>
+  <si>
+    <t>HAK</t>
+  </si>
+  <si>
+    <t>00:40</t>
+  </si>
+  <si>
+    <t>VN-A677</t>
+  </si>
+  <si>
+    <t>06:25</t>
+  </si>
+  <si>
+    <t>09:34</t>
+  </si>
+  <si>
+    <t>02:10</t>
+  </si>
+  <si>
+    <t>03:00</t>
+  </si>
+  <si>
+    <t>04:35</t>
+  </si>
+  <si>
+    <t>VN-A683</t>
+  </si>
+  <si>
+    <t>07:38</t>
+  </si>
+  <si>
+    <t>19:55</t>
+  </si>
+  <si>
+    <t>23:55</t>
+  </si>
+  <si>
+    <t>VN-A684</t>
+  </si>
+  <si>
+    <t>07:00</t>
+  </si>
+  <si>
+    <t>11:08</t>
+  </si>
+  <si>
+    <t>13:13</t>
+  </si>
+  <si>
+    <t>22:30</t>
+  </si>
+  <si>
+    <t>01:10</t>
+  </si>
+  <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>VN-A685</t>
+  </si>
+  <si>
+    <t>10:19</t>
+  </si>
+  <si>
+    <t>12:33</t>
+  </si>
+  <si>
     <t>21:00</t>
   </si>
   <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>06:35</t>
-  </si>
-  <si>
-    <t>BMV</t>
-  </si>
-  <si>
-    <t>07:20</t>
-  </si>
-  <si>
-    <t>08:42</t>
-  </si>
-  <si>
-    <t>09:15</t>
-  </si>
-  <si>
-    <t>10:38</t>
-  </si>
-  <si>
-    <t>12:40</t>
-  </si>
-  <si>
-    <t>20:55</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>06:30</t>
-  </si>
-  <si>
-    <t>DVO</t>
-  </si>
-  <si>
-    <t>23:45</t>
-  </si>
-  <si>
-    <t>VN-A634</t>
-  </si>
-  <si>
-    <t>05:45</t>
-  </si>
-  <si>
-    <t>08:05</t>
-  </si>
-  <si>
-    <t>10:14</t>
-  </si>
-  <si>
-    <t>21:25</t>
-  </si>
-  <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>08:54</t>
-  </si>
-  <si>
-    <t>11:27</t>
-  </si>
-  <si>
-    <t>MFM</t>
-  </si>
-  <si>
-    <t>21:55</t>
-  </si>
-  <si>
-    <t>VN-A637</t>
-  </si>
-  <si>
-    <t>08:12</t>
-  </si>
-  <si>
-    <t>10:21</t>
-  </si>
-  <si>
-    <t>19:35</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>KUL</t>
-  </si>
-  <si>
-    <t>12:35</t>
-  </si>
-  <si>
-    <t>12:32</t>
-  </si>
-  <si>
-    <t>15:20</t>
-  </si>
-  <si>
-    <t>16:15</t>
-  </si>
-  <si>
-    <t>20:45</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>08:25</t>
-  </si>
-  <si>
-    <t>09:42</t>
-  </si>
-  <si>
-    <t>10:05</t>
-  </si>
-  <si>
-    <t>11:22</t>
-  </si>
-  <si>
-    <t>12:05</t>
-  </si>
-  <si>
-    <t>PVG</t>
-  </si>
-  <si>
-    <t>02:15</t>
-  </si>
-  <si>
-    <t>05:25</t>
-  </si>
-  <si>
-    <t>VN-A642</t>
-  </si>
-  <si>
-    <t>07:55</t>
-  </si>
-  <si>
-    <t>09:19</t>
-  </si>
-  <si>
-    <t>09:45</t>
-  </si>
-  <si>
-    <t>11:02</t>
-  </si>
-  <si>
-    <t>12:46</t>
-  </si>
-  <si>
-    <t>VN-A644</t>
-  </si>
-  <si>
-    <t>FUK</t>
-  </si>
-  <si>
-    <t>11:45</t>
-  </si>
-  <si>
-    <t>12:39</t>
-  </si>
-  <si>
-    <t>RMQ</t>
-  </si>
-  <si>
-    <t>VN-A645</t>
-  </si>
-  <si>
-    <t>07:40</t>
-  </si>
-  <si>
-    <t>07:39</t>
-  </si>
-  <si>
-    <t>09:52</t>
-  </si>
-  <si>
-    <t>12:13</t>
-  </si>
-  <si>
-    <t>15:05</t>
-  </si>
-  <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>VN-A646</t>
-  </si>
-  <si>
-    <t>12:55</t>
-  </si>
-  <si>
-    <t>13:17</t>
-  </si>
-  <si>
-    <t>13:25</t>
-  </si>
-  <si>
-    <t>VN-A647</t>
-  </si>
-  <si>
-    <t>10:12</t>
-  </si>
-  <si>
-    <t>VN-A648</t>
-  </si>
-  <si>
-    <t>13:57</t>
-  </si>
-  <si>
-    <t>VN-A649</t>
-  </si>
-  <si>
-    <t>14:51</t>
-  </si>
-  <si>
-    <t>01:40</t>
-  </si>
-  <si>
-    <t>VN-A651</t>
-  </si>
-  <si>
-    <t>09:08</t>
-  </si>
-  <si>
-    <t>11:17</t>
-  </si>
-  <si>
-    <t>17:30</t>
-  </si>
-  <si>
-    <t>VN-A653</t>
-  </si>
-  <si>
-    <t>11:57</t>
-  </si>
-  <si>
-    <t>HND</t>
-  </si>
-  <si>
-    <t>02:00</t>
-  </si>
-  <si>
-    <t>06:10</t>
-  </si>
-  <si>
-    <t>VN-A656</t>
-  </si>
-  <si>
-    <t>VN-A657</t>
-  </si>
-  <si>
-    <t>22:25</t>
-  </si>
-  <si>
-    <t>VN-A658</t>
-  </si>
-  <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>07:29</t>
-  </si>
-  <si>
-    <t>11:50</t>
-  </si>
-  <si>
-    <t>11:38</t>
-  </si>
-  <si>
-    <t>ENH</t>
-  </si>
-  <si>
-    <t>21:15</t>
-  </si>
-  <si>
-    <t>01:15</t>
-  </si>
-  <si>
-    <t>02:20</t>
-  </si>
-  <si>
-    <t>04:50</t>
-  </si>
-  <si>
-    <t>VN-A661</t>
-  </si>
-  <si>
-    <t>12:38</t>
-  </si>
-  <si>
-    <t>13:45</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>21:45</t>
-  </si>
-  <si>
-    <t>02:30</t>
-  </si>
-  <si>
-    <t>04:10</t>
-  </si>
-  <si>
-    <t>VN-A663</t>
-  </si>
-  <si>
-    <t>FSZ</t>
-  </si>
-  <si>
-    <t>13:56</t>
-  </si>
-  <si>
-    <t>14:40</t>
-  </si>
-  <si>
-    <t>CMB</t>
-  </si>
-  <si>
-    <t>21:50</t>
-  </si>
-  <si>
-    <t>VN-A667</t>
-  </si>
-  <si>
-    <t>13:29</t>
-  </si>
-  <si>
-    <t>VN-A668</t>
-  </si>
-  <si>
-    <t>09:44</t>
-  </si>
-  <si>
-    <t>12:09</t>
-  </si>
-  <si>
-    <t>VCL</t>
-  </si>
-  <si>
-    <t>23:30</t>
-  </si>
-  <si>
-    <t>VN-A669</t>
-  </si>
-  <si>
-    <t>HIJ</t>
-  </si>
-  <si>
-    <t>16:14</t>
-  </si>
-  <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>03:55</t>
-  </si>
-  <si>
-    <t>VN-A670</t>
-  </si>
-  <si>
-    <t>05:50</t>
-  </si>
-  <si>
-    <t>07:21</t>
-  </si>
-  <si>
-    <t>11:26</t>
-  </si>
-  <si>
-    <t>12:57</t>
-  </si>
-  <si>
-    <t>MNL</t>
-  </si>
-  <si>
-    <t>02:40</t>
-  </si>
-  <si>
-    <t>03:35</t>
-  </si>
-  <si>
-    <t>04:55</t>
-  </si>
-  <si>
-    <t>VN-A675</t>
-  </si>
-  <si>
-    <t>11:06</t>
-  </si>
-  <si>
-    <t>21:40</t>
-  </si>
-  <si>
-    <t>VN-A676</t>
-  </si>
-  <si>
-    <t>HAK</t>
-  </si>
-  <si>
-    <t>00:40</t>
-  </si>
-  <si>
-    <t>VN-A677</t>
-  </si>
-  <si>
-    <t>06:25</t>
-  </si>
-  <si>
-    <t>09:34</t>
-  </si>
-  <si>
-    <t>02:10</t>
-  </si>
-  <si>
-    <t>03:00</t>
-  </si>
-  <si>
-    <t>04:35</t>
-  </si>
-  <si>
-    <t>VN-A683</t>
-  </si>
-  <si>
-    <t>07:38</t>
-  </si>
-  <si>
-    <t>19:55</t>
-  </si>
-  <si>
-    <t>23:55</t>
-  </si>
-  <si>
-    <t>VN-A684</t>
-  </si>
-  <si>
-    <t>07:00</t>
-  </si>
-  <si>
-    <t>11:08</t>
-  </si>
-  <si>
-    <t>13:13</t>
-  </si>
-  <si>
-    <t>22:30</t>
-  </si>
-  <si>
-    <t>01:10</t>
-  </si>
-  <si>
-    <t>03:05</t>
-  </si>
-  <si>
-    <t>VN-A685</t>
-  </si>
-  <si>
-    <t>10:19</t>
-  </si>
-  <si>
-    <t>12:33</t>
-  </si>
-  <si>
-    <t>22:00</t>
-  </si>
-  <si>
     <t>VN-A687</t>
   </si>
   <si>
@@ -1358,9 +1364,6 @@
     <t>OVB</t>
   </si>
   <si>
-    <t>21:10</t>
-  </si>
-  <si>
     <t>VN-A811</t>
   </si>
   <si>
@@ -1412,7 +1415,7 @@
     <t>Total Record(s): 331</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 20, 2026 12:00</t>
+    <t xml:space="preserve">Generated on  Oct 20, 2026 12:06</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -6104,7 +6107,7 @@
         <v>13</v>
       </c>
       <c r="B141" s="7">
-        <v>280</v>
+        <v>362</v>
       </c>
       <c t="s" r="C141" s="7">
         <v>14</v>
@@ -6120,13 +6123,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H141" s="8">
-        <v>58</v>
+        <v>242</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>203</v>
+        <v>255</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
@@ -6137,7 +6140,7 @@
         <v>13</v>
       </c>
       <c r="B142" s="7">
-        <v>281</v>
+        <v>363</v>
       </c>
       <c t="s" r="C142" s="7">
         <v>14</v>
@@ -6150,32 +6153,50 @@
         <v>321</v>
       </c>
       <c t="s" r="G142" s="8">
-        <v>58</v>
+        <v>242</v>
       </c>
       <c t="s" r="H142" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>223</v>
+        <v>105</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>37</v>
+        <v>130</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
       <c r="M142" s="7"/>
     </row>
     <row r="143" ht="14.25" customHeight="1">
-      <c r="A143" s="6"/>
-      <c r="B143" s="7"/>
-      <c r="C143" s="7"/>
+      <c t="s" r="A143" s="6">
+        <v>13</v>
+      </c>
+      <c r="B143" s="7">
+        <v>642</v>
+      </c>
+      <c t="s" r="C143" s="7">
+        <v>14</v>
+      </c>
       <c r="D143" s="7"/>
-      <c r="E143" s="7"/>
-      <c r="F143" s="7"/>
-      <c r="G143" s="8"/>
-      <c r="H143" s="8"/>
-      <c r="I143" s="7"/>
-      <c r="J143" s="7"/>
+      <c t="s" r="E143" s="7">
+        <v>252</v>
+      </c>
+      <c r="F143" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G143" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="H143" s="8">
+        <v>100</v>
+      </c>
+      <c t="s" r="I143" s="7">
+        <v>110</v>
+      </c>
+      <c t="s" r="J143" s="7">
+        <v>196</v>
+      </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
       <c r="M143" s="7"/>
@@ -6185,84 +6206,62 @@
         <v>13</v>
       </c>
       <c r="B144" s="7">
-        <v>124</v>
+        <v>643</v>
       </c>
       <c t="s" r="C144" s="7">
         <v>14</v>
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G144" s="8">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c t="s" r="H144" s="8">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c t="s" r="I144" s="7">
+        <v>25</v>
+      </c>
+      <c t="s" r="J144" s="7">
         <v>257</v>
-      </c>
-      <c t="s" r="J144" s="7">
-        <v>161</v>
       </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
-      <c t="s" r="M144" s="7">
-        <v>28</v>
-      </c>
+      <c r="M144" s="7"/>
     </row>
     <row r="145" ht="15" customHeight="1">
-      <c t="s" r="A145" s="6">
-        <v>13</v>
-      </c>
-      <c r="B145" s="7">
-        <v>129</v>
-      </c>
-      <c t="s" r="C145" s="7">
-        <v>14</v>
-      </c>
+      <c r="A145" s="6"/>
+      <c r="B145" s="7"/>
+      <c r="C145" s="7"/>
       <c r="D145" s="7"/>
-      <c t="s" r="E145" s="7">
-        <v>256</v>
-      </c>
-      <c r="F145" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G145" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H145" s="8">
-        <v>30</v>
-      </c>
-      <c t="s" r="I145" s="7">
-        <v>32</v>
-      </c>
-      <c t="s" r="J145" s="7">
-        <v>258</v>
-      </c>
+      <c r="E145" s="7"/>
+      <c r="F145" s="7"/>
+      <c r="G145" s="8"/>
+      <c r="H145" s="8"/>
+      <c r="I145" s="7"/>
+      <c r="J145" s="7"/>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
-      <c t="s" r="M145" s="7">
-        <v>259</v>
-      </c>
+      <c r="M145" s="7"/>
     </row>
     <row r="146" ht="14.25" customHeight="1">
       <c t="s" r="A146" s="6">
         <v>13</v>
       </c>
       <c r="B146" s="7">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c t="s" r="C146" s="7">
         <v>14</v>
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6274,17 +6273,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>146</v>
+        <v>259</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>20</v>
-      </c>
-      <c t="s" r="K146" s="7">
-        <v>165</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="K146" s="7"/>
       <c r="L146" s="7"/>
       <c t="s" r="M146" s="7">
-        <v>44</v>
+        <v>28</v>
       </c>
     </row>
     <row r="147" ht="14.25" customHeight="1">
@@ -6292,14 +6289,14 @@
         <v>13</v>
       </c>
       <c r="B147" s="7">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c t="s" r="C147" s="7">
         <v>14</v>
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6311,28 +6308,30 @@
         <v>30</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>254</v>
+        <v>32</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>150</v>
+        <v>260</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
-      <c r="M147" s="7"/>
+      <c t="s" r="M147" s="7">
+        <v>261</v>
+      </c>
     </row>
     <row r="148" ht="14.25" customHeight="1">
       <c t="s" r="A148" s="6">
         <v>13</v>
       </c>
       <c r="B148" s="7">
-        <v>331</v>
+        <v>134</v>
       </c>
       <c t="s" r="C148" s="7">
         <v>14</v>
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6341,46 +6340,50 @@
         <v>30</v>
       </c>
       <c t="s" r="H148" s="8">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>151</v>
-      </c>
-      <c r="K148" s="7"/>
+        <v>20</v>
+      </c>
+      <c t="s" r="K148" s="7">
+        <v>165</v>
+      </c>
       <c r="L148" s="7"/>
-      <c r="M148" s="7"/>
+      <c t="s" r="M148" s="7">
+        <v>44</v>
+      </c>
     </row>
     <row r="149" ht="14.25" customHeight="1">
       <c t="s" r="A149" s="6">
         <v>13</v>
       </c>
       <c r="B149" s="7">
-        <v>328</v>
+        <v>141</v>
       </c>
       <c t="s" r="C149" s="7">
         <v>14</v>
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G149" s="8">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c t="s" r="H149" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>207</v>
+        <v>254</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>209</v>
+        <v>150</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -6391,14 +6394,14 @@
         <v>13</v>
       </c>
       <c r="B150" s="7">
-        <v>160</v>
+        <v>331</v>
       </c>
       <c t="s" r="C150" s="7">
         <v>14</v>
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6407,29 +6410,47 @@
         <v>30</v>
       </c>
       <c t="s" r="H150" s="8">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>260</v>
+        <v>108</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>197</v>
+        <v>151</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
       <c r="M150" s="7"/>
     </row>
     <row r="151" ht="14.25" customHeight="1">
-      <c r="A151" s="6"/>
-      <c r="B151" s="7"/>
-      <c r="C151" s="7"/>
+      <c t="s" r="A151" s="6">
+        <v>13</v>
+      </c>
+      <c r="B151" s="7">
+        <v>328</v>
+      </c>
+      <c t="s" r="C151" s="7">
+        <v>14</v>
+      </c>
       <c r="D151" s="7"/>
-      <c r="E151" s="7"/>
-      <c r="F151" s="7"/>
-      <c r="G151" s="8"/>
-      <c r="H151" s="8"/>
-      <c r="I151" s="7"/>
-      <c r="J151" s="7"/>
+      <c t="s" r="E151" s="7">
+        <v>258</v>
+      </c>
+      <c r="F151" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G151" s="8">
+        <v>73</v>
+      </c>
+      <c t="s" r="H151" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="I151" s="7">
+        <v>207</v>
+      </c>
+      <c t="s" r="J151" s="7">
+        <v>209</v>
+      </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
       <c r="M151" s="7"/>
@@ -6439,78 +6460,78 @@
         <v>13</v>
       </c>
       <c r="B152" s="7">
-        <v>973</v>
+        <v>160</v>
       </c>
       <c t="s" r="C152" s="7">
         <v>14</v>
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G152" s="8">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c t="s" r="H152" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I152" s="7">
         <v>262</v>
       </c>
-      <c t="s" r="I152" s="7">
-        <v>202</v>
-      </c>
       <c t="s" r="J152" s="7">
-        <v>80</v>
+        <v>197</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
       <c r="M152" s="7"/>
     </row>
     <row r="153" ht="14.25" customHeight="1">
-      <c t="s" r="A153" s="6">
-        <v>13</v>
-      </c>
-      <c r="B153" s="7">
-        <v>814</v>
-      </c>
-      <c t="s" r="C153" s="7">
-        <v>14</v>
-      </c>
+      <c r="A153" s="6"/>
+      <c r="B153" s="7"/>
+      <c r="C153" s="7"/>
       <c r="D153" s="7"/>
-      <c t="s" r="E153" s="7">
-        <v>261</v>
-      </c>
-      <c r="F153" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G153" s="8">
-        <v>262</v>
-      </c>
-      <c t="s" r="H153" s="8">
-        <v>30</v>
-      </c>
-      <c t="s" r="I153" s="7">
-        <v>263</v>
-      </c>
-      <c t="s" r="J153" s="7">
-        <v>70</v>
-      </c>
+      <c r="E153" s="7"/>
+      <c r="F153" s="7"/>
+      <c r="G153" s="8"/>
+      <c r="H153" s="8"/>
+      <c r="I153" s="7"/>
+      <c r="J153" s="7"/>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
       <c r="M153" s="7"/>
     </row>
     <row r="154" ht="14.25" customHeight="1">
-      <c r="A154" s="6"/>
-      <c r="B154" s="7"/>
-      <c r="C154" s="7"/>
+      <c t="s" r="A154" s="6">
+        <v>13</v>
+      </c>
+      <c r="B154" s="7">
+        <v>973</v>
+      </c>
+      <c t="s" r="C154" s="7">
+        <v>14</v>
+      </c>
       <c r="D154" s="7"/>
-      <c r="E154" s="7"/>
-      <c r="F154" s="7"/>
-      <c r="G154" s="8"/>
-      <c r="H154" s="8"/>
-      <c r="I154" s="7"/>
-      <c r="J154" s="7"/>
+      <c t="s" r="E154" s="7">
+        <v>263</v>
+      </c>
+      <c r="F154" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G154" s="8">
+        <v>100</v>
+      </c>
+      <c t="s" r="H154" s="8">
+        <v>264</v>
+      </c>
+      <c t="s" r="I154" s="7">
+        <v>202</v>
+      </c>
+      <c t="s" r="J154" s="7">
+        <v>80</v>
+      </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
       <c r="M154" s="7"/>
@@ -6520,108 +6541,82 @@
         <v>13</v>
       </c>
       <c r="B155" s="7">
-        <v>981</v>
+        <v>814</v>
       </c>
       <c t="s" r="C155" s="7">
         <v>14</v>
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
+        <v>263</v>
+      </c>
+      <c r="F155" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G155" s="8">
         <v>264</v>
       </c>
-      <c r="F155" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G155" s="8">
-        <v>53</v>
-      </c>
       <c t="s" r="H155" s="8">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>54</v>
+        <v>265</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>265</v>
+        <v>70</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
-      <c t="s" r="M155" s="7">
-        <v>266</v>
-      </c>
+      <c r="M155" s="7"/>
     </row>
     <row r="156" ht="14.25" customHeight="1">
-      <c t="s" r="A156" s="6">
-        <v>13</v>
-      </c>
-      <c r="B156" s="7">
-        <v>463</v>
-      </c>
-      <c t="s" r="C156" s="7">
-        <v>14</v>
-      </c>
+      <c r="A156" s="6"/>
+      <c r="B156" s="7"/>
+      <c r="C156" s="7"/>
       <c r="D156" s="7"/>
-      <c t="s" r="E156" s="7">
-        <v>264</v>
-      </c>
-      <c r="F156" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G156" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H156" s="8">
-        <v>236</v>
-      </c>
-      <c t="s" r="I156" s="7">
-        <v>218</v>
-      </c>
-      <c t="s" r="J156" s="7">
-        <v>155</v>
-      </c>
-      <c t="s" r="K156" s="7">
-        <v>267</v>
-      </c>
+      <c r="E156" s="7"/>
+      <c r="F156" s="7"/>
+      <c r="G156" s="8"/>
+      <c r="H156" s="8"/>
+      <c r="I156" s="7"/>
+      <c r="J156" s="7"/>
+      <c r="K156" s="7"/>
       <c r="L156" s="7"/>
-      <c t="s" r="M156" s="7">
-        <v>136</v>
-      </c>
+      <c r="M156" s="7"/>
     </row>
     <row r="157" ht="14.25" customHeight="1">
       <c t="s" r="A157" s="6">
         <v>13</v>
       </c>
       <c r="B157" s="7">
-        <v>464</v>
+        <v>981</v>
       </c>
       <c t="s" r="C157" s="7">
         <v>14</v>
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G157" s="8">
-        <v>236</v>
+        <v>53</v>
       </c>
       <c t="s" r="H157" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>268</v>
-      </c>
-      <c t="s" r="K157" s="7">
-        <v>136</v>
-      </c>
+        <v>267</v>
+      </c>
+      <c r="K157" s="7"/>
       <c r="L157" s="7"/>
       <c t="s" r="M157" s="7">
-        <v>106</v>
+        <v>268</v>
       </c>
     </row>
     <row r="158" ht="14.25" customHeight="1">
@@ -6629,14 +6624,14 @@
         <v>13</v>
       </c>
       <c r="B158" s="7">
-        <v>439</v>
+        <v>463</v>
       </c>
       <c t="s" r="C158" s="7">
         <v>14</v>
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6645,20 +6640,20 @@
         <v>17</v>
       </c>
       <c t="s" r="H158" s="8">
-        <v>186</v>
+        <v>236</v>
       </c>
       <c t="s" r="I158" s="7">
+        <v>218</v>
+      </c>
+      <c t="s" r="J158" s="7">
+        <v>155</v>
+      </c>
+      <c t="s" r="K158" s="7">
         <v>269</v>
-      </c>
-      <c t="s" r="J158" s="7">
-        <v>255</v>
-      </c>
-      <c t="s" r="K158" s="7">
-        <v>195</v>
       </c>
       <c r="L158" s="7"/>
       <c t="s" r="M158" s="7">
-        <v>61</v>
+        <v>136</v>
       </c>
     </row>
     <row r="159" ht="14.25" customHeight="1">
@@ -6666,136 +6661,140 @@
         <v>13</v>
       </c>
       <c r="B159" s="7">
-        <v>438</v>
+        <v>464</v>
       </c>
       <c t="s" r="C159" s="7">
         <v>14</v>
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G159" s="8">
-        <v>186</v>
+        <v>236</v>
       </c>
       <c t="s" r="H159" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>223</v>
+        <v>43</v>
       </c>
       <c t="s" r="J159" s="7">
         <v>270</v>
       </c>
       <c t="s" r="K159" s="7">
-        <v>70</v>
+        <v>136</v>
       </c>
       <c r="L159" s="7"/>
       <c t="s" r="M159" s="7">
-        <v>82</v>
+        <v>106</v>
       </c>
     </row>
     <row r="160" ht="15" customHeight="1">
-      <c r="A160" s="6"/>
-      <c r="B160" s="7"/>
-      <c r="C160" s="7"/>
+      <c t="s" r="A160" s="6">
+        <v>13</v>
+      </c>
+      <c r="B160" s="7">
+        <v>439</v>
+      </c>
+      <c t="s" r="C160" s="7">
+        <v>14</v>
+      </c>
       <c r="D160" s="7"/>
-      <c r="E160" s="7"/>
-      <c r="F160" s="7"/>
-      <c r="G160" s="8"/>
-      <c r="H160" s="8"/>
-      <c r="I160" s="7"/>
-      <c r="J160" s="7"/>
-      <c r="K160" s="7"/>
+      <c t="s" r="E160" s="7">
+        <v>266</v>
+      </c>
+      <c r="F160" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G160" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H160" s="8">
+        <v>186</v>
+      </c>
+      <c t="s" r="I160" s="7">
+        <v>271</v>
+      </c>
+      <c t="s" r="J160" s="7">
+        <v>272</v>
+      </c>
+      <c t="s" r="K160" s="7">
+        <v>195</v>
+      </c>
       <c r="L160" s="7"/>
-      <c r="M160" s="7"/>
+      <c t="s" r="M160" s="7">
+        <v>61</v>
+      </c>
     </row>
     <row r="161" ht="14.25" customHeight="1">
       <c t="s" r="A161" s="6">
         <v>13</v>
       </c>
       <c r="B161" s="7">
-        <v>632</v>
+        <v>438</v>
       </c>
       <c t="s" r="C161" s="7">
         <v>14</v>
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G161" s="8">
-        <v>30</v>
+        <v>186</v>
       </c>
       <c t="s" r="H161" s="8">
-        <v>100</v>
+        <v>17</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>272</v>
+        <v>223</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>144</v>
-      </c>
-      <c r="K161" s="7"/>
+        <v>273</v>
+      </c>
+      <c t="s" r="K161" s="7">
+        <v>70</v>
+      </c>
       <c r="L161" s="7"/>
       <c t="s" r="M161" s="7">
-        <v>190</v>
+        <v>82</v>
       </c>
     </row>
     <row r="162" ht="14.25" customHeight="1">
-      <c t="s" r="A162" s="6">
-        <v>13</v>
-      </c>
-      <c r="B162" s="7">
-        <v>629</v>
-      </c>
-      <c t="s" r="C162" s="7">
-        <v>14</v>
-      </c>
+      <c r="A162" s="6"/>
+      <c r="B162" s="7"/>
+      <c r="C162" s="7"/>
       <c r="D162" s="7"/>
-      <c t="s" r="E162" s="7">
-        <v>271</v>
-      </c>
-      <c r="F162" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G162" s="8">
-        <v>100</v>
-      </c>
-      <c t="s" r="H162" s="8">
-        <v>30</v>
-      </c>
-      <c t="s" r="I162" s="7">
-        <v>238</v>
-      </c>
-      <c t="s" r="J162" s="7">
-        <v>192</v>
-      </c>
+      <c r="E162" s="7"/>
+      <c r="F162" s="7"/>
+      <c r="G162" s="8"/>
+      <c r="H162" s="8"/>
+      <c r="I162" s="7"/>
+      <c r="J162" s="7"/>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
-      <c t="s" r="M162" s="7">
-        <v>273</v>
-      </c>
+      <c r="M162" s="7"/>
     </row>
     <row r="163" ht="14.25" customHeight="1">
       <c t="s" r="A163" s="6">
         <v>13</v>
       </c>
       <c r="B163" s="7">
-        <v>807</v>
+        <v>632</v>
       </c>
       <c t="s" r="C163" s="7">
         <v>14</v>
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
@@ -6804,64 +6803,68 @@
         <v>30</v>
       </c>
       <c t="s" r="H163" s="8">
-        <v>274</v>
+        <v>100</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>120</v>
+        <v>275</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>275</v>
+        <v>144</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
-      <c r="M163" s="7"/>
+      <c t="s" r="M163" s="7">
+        <v>190</v>
+      </c>
     </row>
     <row r="164" ht="14.25" customHeight="1">
       <c t="s" r="A164" s="6">
         <v>13</v>
       </c>
       <c r="B164" s="7">
-        <v>800</v>
+        <v>629</v>
       </c>
       <c t="s" r="C164" s="7">
         <v>14</v>
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G164" s="8">
-        <v>274</v>
+        <v>100</v>
       </c>
       <c t="s" r="H164" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>204</v>
+        <v>238</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>255</v>
+        <v>192</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
-      <c r="M164" s="7"/>
+      <c t="s" r="M164" s="7">
+        <v>276</v>
+      </c>
     </row>
     <row r="165" ht="15" customHeight="1">
       <c t="s" r="A165" s="6">
         <v>13</v>
       </c>
       <c r="B165" s="7">
-        <v>216</v>
+        <v>807</v>
       </c>
       <c t="s" r="C165" s="7">
         <v>14</v>
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -6870,13 +6873,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H165" s="8">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
@@ -6887,45 +6890,63 @@
         <v>13</v>
       </c>
       <c r="B166" s="7">
-        <v>217</v>
+        <v>800</v>
       </c>
       <c t="s" r="C166" s="7">
         <v>14</v>
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G166" s="8">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c t="s" r="H166" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>277</v>
+        <v>204</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>87</v>
+        <v>272</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
       <c r="M166" s="7"/>
     </row>
     <row r="167" ht="14.25" customHeight="1">
-      <c r="A167" s="6"/>
-      <c r="B167" s="7"/>
-      <c r="C167" s="7"/>
+      <c t="s" r="A167" s="6">
+        <v>13</v>
+      </c>
+      <c r="B167" s="7">
+        <v>352</v>
+      </c>
+      <c t="s" r="C167" s="7">
+        <v>14</v>
+      </c>
       <c r="D167" s="7"/>
-      <c r="E167" s="7"/>
-      <c r="F167" s="7"/>
-      <c r="G167" s="8"/>
-      <c r="H167" s="8"/>
-      <c r="I167" s="7"/>
-      <c r="J167" s="7"/>
+      <c t="s" r="E167" s="7">
+        <v>274</v>
+      </c>
+      <c r="F167" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G167" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="H167" s="8">
+        <v>279</v>
+      </c>
+      <c t="s" r="I167" s="7">
+        <v>137</v>
+      </c>
+      <c t="s" r="J167" s="7">
+        <v>86</v>
+      </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
       <c r="M167" s="7"/>
@@ -6935,104 +6956,82 @@
         <v>13</v>
       </c>
       <c r="B168" s="7">
-        <v>224</v>
+        <v>353</v>
       </c>
       <c t="s" r="C168" s="7">
         <v>14</v>
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G168" s="8">
-        <v>30</v>
+        <v>279</v>
       </c>
       <c t="s" r="H168" s="8">
-        <v>276</v>
+        <v>30</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>215</v>
+        <v>37</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>143</v>
+        <v>280</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
-      <c t="s" r="M168" s="7">
-        <v>279</v>
-      </c>
+      <c r="M168" s="7"/>
     </row>
     <row r="169" ht="14.25" customHeight="1">
-      <c t="s" r="A169" s="6">
-        <v>13</v>
-      </c>
-      <c r="B169" s="7">
-        <v>741</v>
-      </c>
-      <c t="s" r="C169" s="7">
-        <v>14</v>
-      </c>
+      <c r="A169" s="6"/>
+      <c r="B169" s="7"/>
+      <c r="C169" s="7"/>
       <c r="D169" s="7"/>
-      <c t="s" r="E169" s="7">
-        <v>278</v>
-      </c>
-      <c r="F169" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G169" s="8">
-        <v>276</v>
-      </c>
-      <c t="s" r="H169" s="8">
-        <v>280</v>
-      </c>
-      <c t="s" r="I169" s="7">
-        <v>281</v>
-      </c>
-      <c t="s" r="J169" s="7">
-        <v>32</v>
-      </c>
+      <c r="E169" s="7"/>
+      <c r="F169" s="7"/>
+      <c r="G169" s="8"/>
+      <c r="H169" s="8"/>
+      <c r="I169" s="7"/>
+      <c r="J169" s="7"/>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
-      <c t="s" r="M169" s="7">
-        <v>282</v>
-      </c>
+      <c r="M169" s="7"/>
     </row>
     <row r="170" ht="15" customHeight="1">
       <c t="s" r="A170" s="6">
         <v>13</v>
       </c>
       <c r="B170" s="7">
-        <v>740</v>
+        <v>224</v>
       </c>
       <c t="s" r="C170" s="7">
         <v>14</v>
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G170" s="8">
-        <v>280</v>
+        <v>30</v>
       </c>
       <c t="s" r="H170" s="8">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>283</v>
+        <v>215</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>265</v>
+        <v>143</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
       <c t="s" r="M170" s="7">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="171" ht="14.25" customHeight="1">
@@ -7040,29 +7039,29 @@
         <v>13</v>
       </c>
       <c r="B171" s="7">
-        <v>227</v>
+        <v>741</v>
       </c>
       <c t="s" r="C171" s="7">
         <v>14</v>
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G171" s="8">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c t="s" r="H171" s="8">
-        <v>30</v>
+        <v>279</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>75</v>
+        <v>284</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
@@ -7075,80 +7074,84 @@
         <v>13</v>
       </c>
       <c r="B172" s="7">
-        <v>252</v>
+        <v>740</v>
       </c>
       <c t="s" r="C172" s="7">
         <v>14</v>
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G172" s="8">
-        <v>30</v>
+        <v>279</v>
       </c>
       <c t="s" r="H172" s="8">
-        <v>142</v>
+        <v>282</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>44</v>
+        <v>286</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
-      <c r="M172" s="7"/>
+      <c t="s" r="M172" s="7">
+        <v>287</v>
+      </c>
     </row>
     <row r="173" ht="14.25" customHeight="1">
       <c t="s" r="A173" s="6">
         <v>13</v>
       </c>
       <c r="B173" s="7">
-        <v>253</v>
+        <v>227</v>
       </c>
       <c t="s" r="C173" s="7">
         <v>14</v>
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G173" s="8">
-        <v>142</v>
+        <v>282</v>
       </c>
       <c t="s" r="H173" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>206</v>
+        <v>43</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
-      <c r="M173" s="7"/>
+      <c t="s" r="M173" s="7">
+        <v>288</v>
+      </c>
     </row>
     <row r="174" ht="14.25" customHeight="1">
       <c t="s" r="A174" s="6">
         <v>13</v>
       </c>
       <c r="B174" s="7">
-        <v>154</v>
+        <v>252</v>
       </c>
       <c t="s" r="C174" s="7">
         <v>14</v>
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -7157,29 +7160,47 @@
         <v>30</v>
       </c>
       <c t="s" r="H174" s="8">
-        <v>17</v>
+        <v>142</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>244</v>
+        <v>44</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>286</v>
+        <v>271</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
       <c r="M174" s="7"/>
     </row>
     <row r="175" ht="15" customHeight="1">
-      <c r="A175" s="6"/>
-      <c r="B175" s="7"/>
-      <c r="C175" s="7"/>
+      <c t="s" r="A175" s="6">
+        <v>13</v>
+      </c>
+      <c r="B175" s="7">
+        <v>253</v>
+      </c>
+      <c t="s" r="C175" s="7">
+        <v>14</v>
+      </c>
       <c r="D175" s="7"/>
-      <c r="E175" s="7"/>
-      <c r="F175" s="7"/>
-      <c r="G175" s="8"/>
-      <c r="H175" s="8"/>
-      <c r="I175" s="7"/>
-      <c r="J175" s="7"/>
+      <c t="s" r="E175" s="7">
+        <v>281</v>
+      </c>
+      <c r="F175" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G175" s="8">
+        <v>142</v>
+      </c>
+      <c t="s" r="H175" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="I175" s="7">
+        <v>106</v>
+      </c>
+      <c t="s" r="J175" s="7">
+        <v>206</v>
+      </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
       <c r="M175" s="7"/>
@@ -7189,14 +7210,14 @@
         <v>13</v>
       </c>
       <c r="B176" s="7">
-        <v>350</v>
+        <v>154</v>
       </c>
       <c t="s" r="C176" s="7">
         <v>14</v>
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -7205,68 +7226,46 @@
         <v>30</v>
       </c>
       <c t="s" r="H176" s="8">
-        <v>280</v>
+        <v>17</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>288</v>
+        <v>244</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>272</v>
+        <v>289</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
-      <c t="s" r="M176" s="7">
-        <v>272</v>
-      </c>
+      <c r="M176" s="7"/>
     </row>
     <row r="177" ht="14.25" customHeight="1">
-      <c t="s" r="A177" s="6">
-        <v>13</v>
-      </c>
-      <c r="B177" s="7">
-        <v>351</v>
-      </c>
-      <c t="s" r="C177" s="7">
-        <v>14</v>
-      </c>
+      <c r="A177" s="6"/>
+      <c r="B177" s="7"/>
+      <c r="C177" s="7"/>
       <c r="D177" s="7"/>
-      <c t="s" r="E177" s="7">
-        <v>287</v>
-      </c>
-      <c r="F177" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G177" s="8">
-        <v>280</v>
-      </c>
-      <c t="s" r="H177" s="8">
-        <v>30</v>
-      </c>
-      <c t="s" r="I177" s="7">
-        <v>28</v>
-      </c>
-      <c t="s" r="J177" s="7">
-        <v>190</v>
-      </c>
+      <c r="E177" s="7"/>
+      <c r="F177" s="7"/>
+      <c r="G177" s="8"/>
+      <c r="H177" s="8"/>
+      <c r="I177" s="7"/>
+      <c r="J177" s="7"/>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
-      <c t="s" r="M177" s="7">
-        <v>99</v>
-      </c>
+      <c r="M177" s="7"/>
     </row>
     <row r="178" ht="14.25" customHeight="1">
       <c t="s" r="A178" s="6">
         <v>13</v>
       </c>
       <c r="B178" s="7">
-        <v>630</v>
+        <v>350</v>
       </c>
       <c t="s" r="C178" s="7">
         <v>14</v>
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -7275,20 +7274,18 @@
         <v>30</v>
       </c>
       <c t="s" r="H178" s="8">
-        <v>100</v>
+        <v>279</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>190</v>
+        <v>291</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>218</v>
-      </c>
-      <c t="s" r="K178" s="7">
-        <v>154</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="K178" s="7"/>
       <c r="L178" s="7"/>
       <c t="s" r="M178" s="7">
-        <v>239</v>
+        <v>275</v>
       </c>
     </row>
     <row r="179" ht="14.25" customHeight="1">
@@ -7296,80 +7293,86 @@
         <v>13</v>
       </c>
       <c r="B179" s="7">
-        <v>2856</v>
+        <v>351</v>
       </c>
       <c t="s" r="C179" s="7">
-        <v>245</v>
+        <v>14</v>
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G179" s="8">
-        <v>100</v>
+        <v>279</v>
       </c>
       <c t="s" r="H179" s="8">
-        <v>289</v>
+        <v>30</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>107</v>
+        <v>190</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
-      <c r="M179" s="7"/>
+      <c t="s" r="M179" s="7">
+        <v>99</v>
+      </c>
     </row>
     <row r="180" ht="15" customHeight="1">
       <c t="s" r="A180" s="6">
         <v>13</v>
       </c>
       <c r="B180" s="7">
-        <v>2857</v>
+        <v>630</v>
       </c>
       <c t="s" r="C180" s="7">
-        <v>245</v>
+        <v>14</v>
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G180" s="8">
-        <v>289</v>
+        <v>30</v>
       </c>
       <c t="s" r="H180" s="8">
         <v>100</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>70</v>
+        <v>190</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>131</v>
-      </c>
-      <c r="K180" s="7"/>
+        <v>218</v>
+      </c>
+      <c t="s" r="K180" s="7">
+        <v>154</v>
+      </c>
       <c r="L180" s="7"/>
-      <c r="M180" s="7"/>
+      <c t="s" r="M180" s="7">
+        <v>239</v>
+      </c>
     </row>
     <row r="181" ht="14.25" customHeight="1">
       <c t="s" r="A181" s="6">
         <v>13</v>
       </c>
       <c r="B181" s="7">
-        <v>878</v>
+        <v>2856</v>
       </c>
       <c t="s" r="C181" s="7">
-        <v>14</v>
+        <v>245</v>
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7378,29 +7381,47 @@
         <v>100</v>
       </c>
       <c t="s" r="H181" s="8">
-        <v>115</v>
+        <v>292</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>290</v>
+        <v>20</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>160</v>
+        <v>107</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
       <c r="M181" s="7"/>
     </row>
     <row r="182" ht="14.25" customHeight="1">
-      <c r="A182" s="6"/>
-      <c r="B182" s="7"/>
-      <c r="C182" s="7"/>
+      <c t="s" r="A182" s="6">
+        <v>13</v>
+      </c>
+      <c r="B182" s="7">
+        <v>2857</v>
+      </c>
+      <c t="s" r="C182" s="7">
+        <v>245</v>
+      </c>
       <c r="D182" s="7"/>
-      <c r="E182" s="7"/>
-      <c r="F182" s="7"/>
-      <c r="G182" s="8"/>
-      <c r="H182" s="8"/>
-      <c r="I182" s="7"/>
-      <c r="J182" s="7"/>
+      <c t="s" r="E182" s="7">
+        <v>290</v>
+      </c>
+      <c r="F182" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G182" s="8">
+        <v>292</v>
+      </c>
+      <c t="s" r="H182" s="8">
+        <v>100</v>
+      </c>
+      <c t="s" r="I182" s="7">
+        <v>70</v>
+      </c>
+      <c t="s" r="J182" s="7">
+        <v>131</v>
+      </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
       <c r="M182" s="7"/>
@@ -7410,84 +7431,62 @@
         <v>13</v>
       </c>
       <c r="B183" s="7">
-        <v>771</v>
+        <v>878</v>
       </c>
       <c t="s" r="C183" s="7">
         <v>14</v>
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G183" s="8">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c t="s" r="H183" s="8">
-        <v>89</v>
+        <v>115</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
-      <c t="s" r="M183" s="7">
-        <v>74</v>
-      </c>
+      <c r="M183" s="7"/>
     </row>
     <row r="184" ht="14.25" customHeight="1">
-      <c t="s" r="A184" s="6">
-        <v>13</v>
-      </c>
-      <c r="B184" s="7">
-        <v>770</v>
-      </c>
-      <c t="s" r="C184" s="7">
-        <v>14</v>
-      </c>
+      <c r="A184" s="6"/>
+      <c r="B184" s="7"/>
+      <c r="C184" s="7"/>
       <c r="D184" s="7"/>
-      <c t="s" r="E184" s="7">
-        <v>291</v>
-      </c>
-      <c r="F184" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G184" s="8">
-        <v>89</v>
-      </c>
-      <c t="s" r="H184" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I184" s="7">
-        <v>293</v>
-      </c>
-      <c t="s" r="J184" s="7">
-        <v>162</v>
-      </c>
+      <c r="E184" s="7"/>
+      <c r="F184" s="7"/>
+      <c r="G184" s="8"/>
+      <c r="H184" s="8"/>
+      <c r="I184" s="7"/>
+      <c r="J184" s="7"/>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
-      <c t="s" r="M184" s="7">
-        <v>294</v>
-      </c>
+      <c r="M184" s="7"/>
     </row>
     <row r="185" ht="15" customHeight="1">
       <c t="s" r="A185" s="6">
         <v>13</v>
       </c>
       <c r="B185" s="7">
-        <v>901</v>
+        <v>771</v>
       </c>
       <c t="s" r="C185" s="7">
         <v>14</v>
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7496,18 +7495,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H185" s="8">
-        <v>274</v>
+        <v>89</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>75</v>
+        <v>295</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
       <c t="s" r="M185" s="7">
-        <v>202</v>
+        <v>74</v>
       </c>
     </row>
     <row r="186" ht="14.25" customHeight="1">
@@ -7515,47 +7514,49 @@
         <v>13</v>
       </c>
       <c r="B186" s="7">
-        <v>902</v>
+        <v>770</v>
       </c>
       <c t="s" r="C186" s="7">
         <v>14</v>
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G186" s="8">
-        <v>274</v>
+        <v>89</v>
       </c>
       <c t="s" r="H186" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>136</v>
+        <v>296</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>243</v>
+        <v>162</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
-      <c r="M186" s="7"/>
+      <c t="s" r="M186" s="7">
+        <v>297</v>
+      </c>
     </row>
     <row r="187" ht="14.25" customHeight="1">
       <c t="s" r="A187" s="6">
         <v>13</v>
       </c>
       <c r="B187" s="7">
-        <v>441</v>
+        <v>901</v>
       </c>
       <c t="s" r="C187" s="7">
         <v>14</v>
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -7564,62 +7565,82 @@
         <v>17</v>
       </c>
       <c t="s" r="H187" s="8">
-        <v>73</v>
+        <v>277</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
-      <c r="M187" s="7"/>
+      <c t="s" r="M187" s="7">
+        <v>202</v>
+      </c>
     </row>
     <row r="188" ht="14.25" customHeight="1">
       <c t="s" r="A188" s="6">
         <v>13</v>
       </c>
       <c r="B188" s="7">
-        <v>442</v>
+        <v>902</v>
       </c>
       <c t="s" r="C188" s="7">
         <v>14</v>
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G188" s="8">
-        <v>73</v>
+        <v>277</v>
       </c>
       <c t="s" r="H188" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>181</v>
+        <v>136</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>295</v>
+        <v>243</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
       <c r="M188" s="7"/>
     </row>
     <row r="189" ht="14.25" customHeight="1">
-      <c r="A189" s="6"/>
-      <c r="B189" s="7"/>
-      <c r="C189" s="7"/>
+      <c t="s" r="A189" s="6">
+        <v>13</v>
+      </c>
+      <c r="B189" s="7">
+        <v>441</v>
+      </c>
+      <c t="s" r="C189" s="7">
+        <v>14</v>
+      </c>
       <c r="D189" s="7"/>
-      <c r="E189" s="7"/>
-      <c r="F189" s="7"/>
-      <c r="G189" s="8"/>
-      <c r="H189" s="8"/>
-      <c r="I189" s="7"/>
-      <c r="J189" s="7"/>
+      <c t="s" r="E189" s="7">
+        <v>294</v>
+      </c>
+      <c r="F189" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G189" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H189" s="8">
+        <v>73</v>
+      </c>
+      <c t="s" r="I189" s="7">
+        <v>105</v>
+      </c>
+      <c t="s" r="J189" s="7">
+        <v>24</v>
+      </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
       <c r="M189" s="7"/>
@@ -7629,84 +7650,62 @@
         <v>13</v>
       </c>
       <c r="B190" s="7">
-        <v>719</v>
+        <v>442</v>
       </c>
       <c t="s" r="C190" s="7">
         <v>14</v>
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G190" s="8">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c t="s" r="H190" s="8">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>65</v>
+        <v>181</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>190</v>
+        <v>298</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
-      <c t="s" r="M190" s="7">
-        <v>297</v>
-      </c>
+      <c r="M190" s="7"/>
     </row>
     <row r="191" ht="14.25" customHeight="1">
-      <c t="s" r="A191" s="6">
-        <v>13</v>
-      </c>
-      <c r="B191" s="7">
-        <v>718</v>
-      </c>
-      <c t="s" r="C191" s="7">
-        <v>14</v>
-      </c>
+      <c r="A191" s="6"/>
+      <c r="B191" s="7"/>
+      <c r="C191" s="7"/>
       <c r="D191" s="7"/>
-      <c t="s" r="E191" s="7">
-        <v>296</v>
-      </c>
-      <c r="F191" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G191" s="8">
-        <v>73</v>
-      </c>
-      <c t="s" r="H191" s="8">
-        <v>100</v>
-      </c>
-      <c t="s" r="I191" s="7">
-        <v>154</v>
-      </c>
-      <c t="s" r="J191" s="7">
-        <v>146</v>
-      </c>
+      <c r="E191" s="7"/>
+      <c r="F191" s="7"/>
+      <c r="G191" s="8"/>
+      <c r="H191" s="8"/>
+      <c r="I191" s="7"/>
+      <c r="J191" s="7"/>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
-      <c t="s" r="M191" s="7">
-        <v>298</v>
-      </c>
+      <c r="M191" s="7"/>
     </row>
     <row r="192" ht="14.25" customHeight="1">
       <c t="s" r="A192" s="6">
         <v>13</v>
       </c>
       <c r="B192" s="7">
-        <v>8890</v>
+        <v>719</v>
       </c>
       <c t="s" r="C192" s="7">
         <v>14</v>
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7715,64 +7714,68 @@
         <v>100</v>
       </c>
       <c t="s" r="H192" s="8">
-        <v>299</v>
+        <v>73</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>192</v>
+        <v>65</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>101</v>
+        <v>190</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
-      <c r="M192" s="7"/>
+      <c t="s" r="M192" s="7">
+        <v>300</v>
+      </c>
     </row>
     <row r="193" ht="14.25" customHeight="1">
       <c t="s" r="A193" s="6">
         <v>13</v>
       </c>
       <c r="B193" s="7">
-        <v>8891</v>
+        <v>718</v>
       </c>
       <c t="s" r="C193" s="7">
         <v>14</v>
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G193" s="8">
-        <v>299</v>
+        <v>73</v>
       </c>
       <c t="s" r="H193" s="8">
         <v>100</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>243</v>
+        <v>154</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>222</v>
+        <v>146</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
-      <c r="M193" s="7"/>
+      <c t="s" r="M193" s="7">
+        <v>301</v>
+      </c>
     </row>
     <row r="194" ht="14.25" customHeight="1">
       <c t="s" r="A194" s="6">
         <v>13</v>
       </c>
       <c r="B194" s="7">
-        <v>8892</v>
+        <v>8890</v>
       </c>
       <c t="s" r="C194" s="7">
         <v>14</v>
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -7781,13 +7784,13 @@
         <v>100</v>
       </c>
       <c t="s" r="H194" s="8">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>137</v>
+        <v>192</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>210</v>
+        <v>101</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -7798,29 +7801,29 @@
         <v>13</v>
       </c>
       <c r="B195" s="7">
-        <v>8893</v>
+        <v>8891</v>
       </c>
       <c t="s" r="C195" s="7">
         <v>14</v>
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G195" s="8">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c t="s" r="H195" s="8">
         <v>100</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>300</v>
+        <v>243</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
@@ -7828,17 +7831,17 @@
     </row>
     <row r="196" ht="14.25" customHeight="1">
       <c t="s" r="A196" s="6">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="B196" s="7">
-        <v>988</v>
+        <v>8892</v>
       </c>
       <c t="s" r="C196" s="7">
         <v>14</v>
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -7847,116 +7850,112 @@
         <v>100</v>
       </c>
       <c t="s" r="H196" s="8">
-        <v>53</v>
+        <v>302</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>27</v>
+        <v>137</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>229</v>
+        <v>210</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
       <c r="M196" s="7"/>
     </row>
     <row r="197" ht="14.25" customHeight="1">
-      <c r="A197" s="6"/>
-      <c r="B197" s="7"/>
-      <c r="C197" s="7"/>
+      <c t="s" r="A197" s="6">
+        <v>13</v>
+      </c>
+      <c r="B197" s="7">
+        <v>8893</v>
+      </c>
+      <c t="s" r="C197" s="7">
+        <v>14</v>
+      </c>
       <c r="D197" s="7"/>
-      <c r="E197" s="7"/>
-      <c r="F197" s="7"/>
-      <c r="G197" s="8"/>
-      <c r="H197" s="8"/>
-      <c r="I197" s="7"/>
-      <c r="J197" s="7"/>
+      <c t="s" r="E197" s="7">
+        <v>299</v>
+      </c>
+      <c r="F197" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G197" s="8">
+        <v>302</v>
+      </c>
+      <c t="s" r="H197" s="8">
+        <v>100</v>
+      </c>
+      <c t="s" r="I197" s="7">
+        <v>303</v>
+      </c>
+      <c t="s" r="J197" s="7">
+        <v>197</v>
+      </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
       <c r="M197" s="7"/>
     </row>
     <row r="198" ht="14.25" customHeight="1">
       <c t="s" r="A198" s="6">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="B198" s="7">
-        <v>260</v>
+        <v>988</v>
       </c>
       <c t="s" r="C198" s="7">
         <v>14</v>
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G198" s="8">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c t="s" r="H198" s="8">
-        <v>129</v>
+        <v>53</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>279</v>
+        <v>27</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>54</v>
+        <v>229</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
-      <c t="s" r="M198" s="7">
-        <v>302</v>
-      </c>
+      <c r="M198" s="7"/>
     </row>
     <row r="199" ht="14.25" customHeight="1">
-      <c t="s" r="A199" s="6">
-        <v>13</v>
-      </c>
-      <c r="B199" s="7">
-        <v>261</v>
-      </c>
-      <c t="s" r="C199" s="7">
-        <v>14</v>
-      </c>
+      <c r="A199" s="6"/>
+      <c r="B199" s="7"/>
+      <c r="C199" s="7"/>
       <c r="D199" s="7"/>
-      <c t="s" r="E199" s="7">
-        <v>301</v>
-      </c>
-      <c r="F199" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G199" s="8">
-        <v>129</v>
-      </c>
-      <c t="s" r="H199" s="8">
-        <v>30</v>
-      </c>
-      <c t="s" r="I199" s="7">
-        <v>134</v>
-      </c>
-      <c t="s" r="J199" s="7">
-        <v>175</v>
-      </c>
+      <c r="E199" s="7"/>
+      <c r="F199" s="7"/>
+      <c r="G199" s="8"/>
+      <c r="H199" s="8"/>
+      <c r="I199" s="7"/>
+      <c r="J199" s="7"/>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
-      <c t="s" r="M199" s="7">
-        <v>303</v>
-      </c>
+      <c r="M199" s="7"/>
     </row>
     <row r="200" ht="15" customHeight="1">
       <c t="s" r="A200" s="6">
         <v>13</v>
       </c>
       <c r="B200" s="7">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c t="s" r="C200" s="7">
         <v>14</v>
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -7965,20 +7964,18 @@
         <v>30</v>
       </c>
       <c t="s" r="H200" s="8">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>193</v>
+        <v>283</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>151</v>
-      </c>
-      <c t="s" r="K200" s="7">
-        <v>170</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="K200" s="7"/>
       <c r="L200" s="7"/>
       <c t="s" r="M200" s="7">
-        <v>70</v>
+        <v>305</v>
       </c>
     </row>
     <row r="201" ht="14.25" customHeight="1">
@@ -7986,117 +7983,121 @@
         <v>13</v>
       </c>
       <c r="B201" s="7">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c t="s" r="C201" s="7">
         <v>14</v>
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G201" s="8">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c t="s" r="H201" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>24</v>
+        <v>134</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>210</v>
-      </c>
-      <c t="s" r="K201" s="7">
-        <v>304</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="K201" s="7"/>
       <c r="L201" s="7"/>
       <c t="s" r="M201" s="7">
-        <v>92</v>
+        <v>306</v>
       </c>
     </row>
     <row r="202" ht="14.25" customHeight="1">
-      <c r="A202" s="6"/>
-      <c r="B202" s="7"/>
-      <c r="C202" s="7"/>
+      <c t="s" r="A202" s="6">
+        <v>13</v>
+      </c>
+      <c r="B202" s="7">
+        <v>254</v>
+      </c>
+      <c t="s" r="C202" s="7">
+        <v>14</v>
+      </c>
       <c r="D202" s="7"/>
-      <c r="E202" s="7"/>
-      <c r="F202" s="7"/>
-      <c r="G202" s="8"/>
-      <c r="H202" s="8"/>
-      <c r="I202" s="7"/>
-      <c r="J202" s="7"/>
-      <c r="K202" s="7"/>
+      <c t="s" r="E202" s="7">
+        <v>304</v>
+      </c>
+      <c r="F202" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G202" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="H202" s="8">
+        <v>142</v>
+      </c>
+      <c t="s" r="I202" s="7">
+        <v>193</v>
+      </c>
+      <c t="s" r="J202" s="7">
+        <v>151</v>
+      </c>
+      <c t="s" r="K202" s="7">
+        <v>170</v>
+      </c>
       <c r="L202" s="7"/>
-      <c r="M202" s="7"/>
+      <c t="s" r="M202" s="7">
+        <v>70</v>
+      </c>
     </row>
     <row r="203" ht="14.25" customHeight="1">
       <c t="s" r="A203" s="6">
         <v>13</v>
       </c>
       <c r="B203" s="7">
-        <v>825</v>
+        <v>255</v>
       </c>
       <c t="s" r="C203" s="7">
         <v>14</v>
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G203" s="8">
-        <v>30</v>
+        <v>142</v>
       </c>
       <c t="s" r="H203" s="8">
-        <v>306</v>
+        <v>30</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c t="s" r="J203" s="7">
+        <v>210</v>
+      </c>
+      <c t="s" r="K203" s="7">
         <v>307</v>
       </c>
-      <c r="K203" s="7"/>
       <c r="L203" s="7"/>
       <c t="s" r="M203" s="7">
-        <v>308</v>
+        <v>92</v>
       </c>
     </row>
     <row r="204" ht="14.25" customHeight="1">
-      <c t="s" r="A204" s="6">
-        <v>13</v>
-      </c>
-      <c r="B204" s="7">
-        <v>826</v>
-      </c>
-      <c t="s" r="C204" s="7">
-        <v>14</v>
-      </c>
+      <c r="A204" s="6"/>
+      <c r="B204" s="7"/>
+      <c r="C204" s="7"/>
       <c r="D204" s="7"/>
-      <c t="s" r="E204" s="7">
-        <v>305</v>
-      </c>
-      <c r="F204" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G204" s="8">
-        <v>306</v>
-      </c>
-      <c t="s" r="H204" s="8">
-        <v>30</v>
-      </c>
-      <c t="s" r="I204" s="7">
-        <v>33</v>
-      </c>
-      <c t="s" r="J204" s="7">
-        <v>148</v>
-      </c>
+      <c r="E204" s="7"/>
+      <c r="F204" s="7"/>
+      <c r="G204" s="8"/>
+      <c r="H204" s="8"/>
+      <c r="I204" s="7"/>
+      <c r="J204" s="7"/>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
       <c r="M204" s="7"/>
@@ -8106,14 +8107,14 @@
         <v>13</v>
       </c>
       <c r="B205" s="7">
-        <v>362</v>
+        <v>825</v>
       </c>
       <c t="s" r="C205" s="7">
         <v>14</v>
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -8122,46 +8123,48 @@
         <v>30</v>
       </c>
       <c t="s" r="H205" s="8">
-        <v>242</v>
+        <v>309</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>309</v>
+        <v>18</v>
       </c>
       <c t="s" r="J205" s="7">
         <v>310</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
-      <c r="M205" s="7"/>
+      <c t="s" r="M205" s="7">
+        <v>311</v>
+      </c>
     </row>
     <row r="206" ht="14.25" customHeight="1">
       <c t="s" r="A206" s="6">
         <v>13</v>
       </c>
       <c r="B206" s="7">
-        <v>363</v>
+        <v>826</v>
       </c>
       <c t="s" r="C206" s="7">
         <v>14</v>
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G206" s="8">
-        <v>242</v>
+        <v>309</v>
       </c>
       <c t="s" r="H206" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>105</v>
+        <v>33</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -8172,14 +8175,14 @@
         <v>13</v>
       </c>
       <c r="B207" s="7">
-        <v>352</v>
+        <v>280</v>
       </c>
       <c t="s" r="C207" s="7">
         <v>14</v>
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -8188,13 +8191,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H207" s="8">
-        <v>280</v>
+        <v>58</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>137</v>
+        <v>203</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>86</v>
+        <v>272</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -8205,29 +8208,29 @@
         <v>13</v>
       </c>
       <c r="B208" s="7">
-        <v>353</v>
+        <v>281</v>
       </c>
       <c t="s" r="C208" s="7">
         <v>14</v>
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G208" s="8">
-        <v>280</v>
+        <v>58</v>
       </c>
       <c t="s" r="H208" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I208" s="7">
+        <v>223</v>
+      </c>
+      <c t="s" r="J208" s="7">
         <v>37</v>
-      </c>
-      <c t="s" r="J208" s="7">
-        <v>311</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -8408,7 +8411,7 @@
         <v>100</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c t="s" r="J214" s="7">
         <v>205</v>
@@ -8558,7 +8561,7 @@
         <v>322</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
@@ -8675,7 +8678,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c t="s" r="J223" s="7">
         <v>329</v>
@@ -8824,7 +8827,7 @@
         <v>186</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c t="s" r="J228" s="7">
         <v>333</v>
@@ -8891,7 +8894,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H230" s="8">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c t="s" r="I230" s="7">
         <v>164</v>
@@ -8923,7 +8926,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G231" s="8">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c t="s" r="H231" s="8">
         <v>17</v>
@@ -9108,7 +9111,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H237" s="8">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c t="s" r="I237" s="7">
         <v>342</v>
@@ -9121,7 +9124,7 @@
       </c>
       <c r="L237" s="7"/>
       <c t="s" r="M237" s="7">
-        <v>310</v>
+        <v>256</v>
       </c>
     </row>
     <row r="238" ht="14.25" customHeight="1">
@@ -9142,7 +9145,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G238" s="8">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c t="s" r="H238" s="8">
         <v>30</v>
@@ -9313,7 +9316,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H244" s="8">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c t="s" r="I244" s="7">
         <v>154</v>
@@ -9345,7 +9348,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G245" s="8">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c t="s" r="H245" s="8">
         <v>17</v>
@@ -9384,10 +9387,10 @@
         <v>100</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>311</v>
+        <v>280</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
@@ -9547,7 +9550,7 @@
       </c>
       <c r="L251" s="7"/>
       <c t="s" r="M251" s="7">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="252" ht="14.25" customHeight="1">
@@ -9622,7 +9625,7 @@
         <v>100</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c t="s" r="J254" s="7">
         <v>144</v>
@@ -9660,7 +9663,7 @@
         <v>145</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c t="s" r="K255" s="7">
         <v>18</v>
@@ -9704,7 +9707,7 @@
       </c>
       <c r="L256" s="7"/>
       <c t="s" r="M256" s="7">
-        <v>120</v>
+        <v>353</v>
       </c>
     </row>
     <row r="257" ht="14.25" customHeight="1">
@@ -9741,7 +9744,7 @@
       </c>
       <c r="L257" s="7"/>
       <c t="s" r="M257" s="7">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="258" ht="14.25" customHeight="1">
@@ -9768,10 +9771,10 @@
         <v>242</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
@@ -9834,14 +9837,18 @@
         <v>30</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c t="s" r="J260" s="7">
         <v>212</v>
       </c>
-      <c r="K260" s="7"/>
+      <c t="s" r="K260" s="7">
+        <v>355</v>
+      </c>
       <c r="L260" s="7"/>
-      <c r="M260" s="7"/>
+      <c t="s" r="M260" s="7">
+        <v>356</v>
+      </c>
     </row>
     <row r="261" ht="14.25" customHeight="1">
       <c r="A261" s="6"/>
@@ -9870,7 +9877,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -9882,7 +9889,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c t="s" r="J262" s="7">
         <v>225</v>
@@ -9890,7 +9897,7 @@
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
       <c t="s" r="M262" s="7">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="263" ht="14.25" customHeight="1">
@@ -9905,7 +9912,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -9917,7 +9924,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c t="s" r="J263" s="7">
         <v>101</v>
@@ -9940,7 +9947,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
@@ -9949,7 +9956,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H264" s="8">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c t="s" r="I264" s="7">
         <v>205</v>
@@ -9973,22 +9980,22 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G265" s="8">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c t="s" r="H265" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
@@ -10021,7 +10028,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F267" s="7">
         <v>320</v>
@@ -10030,7 +10037,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H267" s="8">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c t="s" r="I267" s="7">
         <v>136</v>
@@ -10058,13 +10065,13 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F268" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G268" s="8">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c t="s" r="H268" s="8">
         <v>30</v>
@@ -10110,7 +10117,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -10125,7 +10132,7 @@
         <v>25</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
@@ -10158,7 +10165,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="F272" s="7">
         <v>320</v>
@@ -10170,7 +10177,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c t="s" r="J272" s="7">
         <v>333</v>
@@ -10178,7 +10185,7 @@
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
       <c t="s" r="M272" s="7">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="273" ht="14.25" customHeight="1">
@@ -10193,7 +10200,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="F273" s="7">
         <v>320</v>
@@ -10208,12 +10215,12 @@
         <v>125</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
       <c t="s" r="M273" s="7">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="274" ht="14.25" customHeight="1">
@@ -10228,7 +10235,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="F274" s="7">
         <v>320</v>
@@ -10237,7 +10244,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H274" s="8">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c t="s" r="I274" s="7">
         <v>136</v>
@@ -10261,13 +10268,13 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="F275" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G275" s="8">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c t="s" r="H275" s="8">
         <v>17</v>
@@ -10276,7 +10283,7 @@
         <v>107</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -10294,7 +10301,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="F276" s="7">
         <v>320</v>
@@ -10306,10 +10313,10 @@
         <v>318</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -10327,7 +10334,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="F277" s="7">
         <v>320</v>
@@ -10339,10 +10346,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -10375,7 +10382,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
@@ -10384,7 +10391,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H279" s="8">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c t="s" r="I279" s="7">
         <v>190</v>
@@ -10395,7 +10402,7 @@
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
       <c t="s" r="M279" s="7">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="280" ht="15" customHeight="1">
@@ -10410,13 +10417,13 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G280" s="8">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c t="s" r="H280" s="8">
         <v>73</v>
@@ -10425,11 +10432,13 @@
         <v>19</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
-      <c r="M280" s="7"/>
+      <c t="s" r="M280" s="7">
+        <v>44</v>
+      </c>
     </row>
     <row r="281" ht="14.25" customHeight="1">
       <c t="s" r="A281" s="6">
@@ -10443,7 +10452,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
@@ -10452,7 +10461,7 @@
         <v>73</v>
       </c>
       <c t="s" r="H281" s="8">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c t="s" r="I281" s="7">
         <v>204</v>
@@ -10476,13 +10485,13 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="F282" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G282" s="8">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c t="s" r="H282" s="8">
         <v>30</v>
@@ -10509,7 +10518,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="F283" s="7">
         <v>321</v>
@@ -10518,10 +10527,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H283" s="8">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c t="s" r="J283" s="7">
         <v>227</v>
@@ -10542,22 +10551,22 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="F284" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G284" s="8">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c t="s" r="H284" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
@@ -10590,13 +10599,13 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="F286" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G286" s="8">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c t="s" r="H286" s="8">
         <v>17</v>
@@ -10610,7 +10619,7 @@
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
       <c t="s" r="M286" s="7">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="287" ht="14.25" customHeight="1">
@@ -10625,7 +10634,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="F287" s="7">
         <v>320</v>
@@ -10637,7 +10646,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c t="s" r="J287" s="7">
         <v>195</v>
@@ -10658,7 +10667,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="F288" s="7">
         <v>320</v>
@@ -10667,20 +10676,20 @@
         <v>30</v>
       </c>
       <c t="s" r="H288" s="8">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c t="s" r="I288" s="7">
         <v>137</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c t="s" r="K288" s="7">
         <v>24</v>
       </c>
       <c r="L288" s="7"/>
       <c t="s" r="M288" s="7">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="289" ht="14.25" customHeight="1">
@@ -10695,13 +10704,13 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="F289" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G289" s="8">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c t="s" r="H289" s="8">
         <v>30</v>
@@ -10717,7 +10726,7 @@
       </c>
       <c r="L289" s="7"/>
       <c t="s" r="M289" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="290" ht="15" customHeight="1">
@@ -10747,7 +10756,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -10756,7 +10765,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H291" s="8">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c t="s" r="I291" s="7">
         <v>216</v>
@@ -10782,13 +10791,13 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G292" s="8">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c t="s" r="H292" s="8">
         <v>100</v>
@@ -10802,7 +10811,7 @@
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
       <c t="s" r="M292" s="7">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="293" ht="14.25" customHeight="1">
@@ -10817,7 +10826,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
@@ -10850,7 +10859,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="F294" s="7">
         <v>321</v>
@@ -10898,7 +10907,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
@@ -10907,7 +10916,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H296" s="8">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c t="s" r="I296" s="7">
         <v>322</v>
@@ -10918,7 +10927,7 @@
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
       <c t="s" r="M296" s="7">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="297" ht="14.25" customHeight="1">
@@ -10933,13 +10942,13 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G297" s="8">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c t="s" r="H297" s="8">
         <v>30</v>
@@ -10953,7 +10962,7 @@
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
       <c t="s" r="M297" s="7">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="298" ht="14.25" customHeight="1">
@@ -10968,7 +10977,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
@@ -10977,7 +10986,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H298" s="8">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c t="s" r="I298" s="7">
         <v>340</v>
@@ -11001,19 +11010,19 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G299" s="8">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c t="s" r="H299" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c t="s" r="J299" s="7">
         <v>127</v>
@@ -11034,7 +11043,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
@@ -11043,7 +11052,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H300" s="8">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c t="s" r="I300" s="7">
         <v>61</v>
@@ -11067,13 +11076,13 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="F301" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G301" s="8">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c t="s" r="H301" s="8">
         <v>30</v>
@@ -11100,7 +11109,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="F302" s="7">
         <v>320</v>
@@ -11122,7 +11131,7 @@
       </c>
       <c r="L302" s="7"/>
       <c t="s" r="M302" s="7">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="303" ht="14.25" customHeight="1">
@@ -11152,7 +11161,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="F304" s="7">
         <v>320</v>
@@ -11161,7 +11170,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H304" s="8">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c t="s" r="I304" s="7">
         <v>251</v>
@@ -11172,7 +11181,7 @@
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
       <c t="s" r="M304" s="7">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="305" ht="15" customHeight="1">
@@ -11187,13 +11196,13 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="F305" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G305" s="8">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c t="s" r="H305" s="8">
         <v>17</v>
@@ -11207,7 +11216,7 @@
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
       <c t="s" r="M305" s="7">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="306" ht="14.25" customHeight="1">
@@ -11222,7 +11231,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="F306" s="7">
         <v>320</v>
@@ -11231,7 +11240,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H306" s="8">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c t="s" r="I306" s="7">
         <v>209</v>
@@ -11255,13 +11264,13 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="F307" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G307" s="8">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c t="s" r="H307" s="8">
         <v>17</v>
@@ -11270,7 +11279,7 @@
         <v>183</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
@@ -11303,7 +11312,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F309" s="7">
         <v>321</v>
@@ -11315,7 +11324,7 @@
         <v>100</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c t="s" r="J309" s="7">
         <v>216</v>
@@ -11323,7 +11332,7 @@
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
       <c t="s" r="M309" s="7">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="310" ht="15" customHeight="1">
@@ -11338,7 +11347,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F310" s="7">
         <v>321</v>
@@ -11358,7 +11367,7 @@
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
       <c t="s" r="M310" s="7">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="311" ht="14.25" customHeight="1">
@@ -11373,7 +11382,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F311" s="7">
         <v>321</v>
@@ -11393,7 +11402,7 @@
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
       <c t="s" r="M311" s="7">
-        <v>401</v>
+        <v>19</v>
       </c>
     </row>
     <row r="312" ht="14.25" customHeight="1">
@@ -11408,7 +11417,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F312" s="7">
         <v>321</v>
@@ -11441,7 +11450,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F313" s="7">
         <v>321</v>
@@ -11474,7 +11483,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F314" s="7">
         <v>321</v>
@@ -11483,13 +11492,13 @@
         <v>100</v>
       </c>
       <c t="s" r="H314" s="8">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c t="s" r="I314" s="7">
         <v>212</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -11507,22 +11516,22 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F315" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G315" s="8">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c t="s" r="H315" s="8">
         <v>100</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
@@ -11555,7 +11564,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
@@ -11590,7 +11599,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
@@ -11602,7 +11611,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c t="s" r="J318" s="7">
         <v>238</v>
@@ -11610,7 +11619,7 @@
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
       <c t="s" r="M318" s="7">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="319" ht="14.25" customHeight="1">
@@ -11625,7 +11634,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F319" s="7">
         <v>320</v>
@@ -11660,7 +11669,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
@@ -11693,7 +11702,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
@@ -11702,10 +11711,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H321" s="8">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c t="s" r="J321" s="7">
         <v>86</v>
@@ -11726,13 +11735,13 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G322" s="8">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c t="s" r="H322" s="8">
         <v>17</v>
@@ -11759,7 +11768,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
@@ -11771,13 +11780,13 @@
         <v>30</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c t="s" r="J323" s="7">
         <v>39</v>
       </c>
       <c t="s" r="K323" s="7">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="L323" s="7"/>
       <c t="s" r="M323" s="7">
@@ -11811,13 +11820,13 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G325" s="8">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c t="s" r="H325" s="8">
         <v>17</v>
@@ -11826,7 +11835,7 @@
         <v>50</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11859,7 +11868,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="F327" s="7">
         <v>321</v>
@@ -11871,7 +11880,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c t="s" r="J327" s="7">
         <v>56</v>
@@ -11879,7 +11888,7 @@
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
       <c t="s" r="M327" s="7">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="328" ht="14.25" customHeight="1">
@@ -11894,7 +11903,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="F328" s="7">
         <v>321</v>
@@ -11929,7 +11938,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="F329" s="7">
         <v>321</v>
@@ -11962,7 +11971,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="F330" s="7">
         <v>321</v>
@@ -11977,7 +11986,7 @@
         <v>70</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
@@ -11995,7 +12004,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="F331" s="7">
         <v>321</v>
@@ -12004,13 +12013,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H331" s="8">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
@@ -12028,22 +12037,22 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="F332" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G332" s="8">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c t="s" r="H332" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
@@ -12076,7 +12085,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="F334" s="7">
         <v>321</v>
@@ -12088,15 +12097,15 @@
         <v>58</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
       <c t="s" r="M334" s="7">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="335" ht="15" customHeight="1">
@@ -12111,7 +12120,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="F335" s="7">
         <v>321</v>
@@ -12120,13 +12129,13 @@
         <v>58</v>
       </c>
       <c t="s" r="H335" s="8">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
@@ -12146,13 +12155,13 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="F336" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G336" s="8">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c t="s" r="H336" s="8">
         <v>58</v>
@@ -12161,7 +12170,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -12179,7 +12188,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="F337" s="7">
         <v>321</v>
@@ -12212,7 +12221,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="F338" s="7">
         <v>321</v>
@@ -12227,7 +12236,7 @@
         <v>23</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
@@ -12245,7 +12254,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="F339" s="7">
         <v>321</v>
@@ -12257,7 +12266,7 @@
         <v>115</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c t="s" r="J339" s="7">
         <v>251</v>
@@ -12293,7 +12302,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="F341" s="7">
         <v>321</v>
@@ -12305,7 +12314,7 @@
         <v>242</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c t="s" r="J341" s="7">
         <v>144</v>
@@ -12328,7 +12337,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="F342" s="7">
         <v>321</v>
@@ -12337,7 +12346,7 @@
         <v>242</v>
       </c>
       <c t="s" r="H342" s="8">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c t="s" r="I342" s="7">
         <v>145</v>
@@ -12350,7 +12359,7 @@
       </c>
       <c r="L342" s="7"/>
       <c t="s" r="M342" s="7">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="343" ht="14.25" customHeight="1">
@@ -12365,13 +12374,13 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="F343" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G343" s="8">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c t="s" r="H343" s="8">
         <v>242</v>
@@ -12385,7 +12394,7 @@
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
       <c t="s" r="M343" s="7">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="344" ht="14.25" customHeight="1">
@@ -12400,7 +12409,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="F344" s="7">
         <v>321</v>
@@ -12433,7 +12442,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="F345" s="7">
         <v>321</v>
@@ -12466,7 +12475,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="F346" s="7">
         <v>321</v>
@@ -12499,7 +12508,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="F347" s="7">
         <v>321</v>
@@ -12508,13 +12517,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H347" s="8">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
@@ -12532,22 +12541,22 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="F348" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G348" s="8">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c t="s" r="H348" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -12580,7 +12589,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="F350" s="7">
         <v>321</v>
@@ -12600,7 +12609,7 @@
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
       <c t="s" r="M350" s="7">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="351" ht="14.25" customHeight="1">
@@ -12615,7 +12624,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
@@ -12635,7 +12644,7 @@
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
       <c t="s" r="M351" s="7">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="352" ht="14.25" customHeight="1">
@@ -12650,7 +12659,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
@@ -12662,7 +12671,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c t="s" r="J352" s="7">
         <v>136</v>
@@ -12683,7 +12692,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
@@ -12716,7 +12725,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
@@ -12742,14 +12751,14 @@
         <v>13</v>
       </c>
       <c r="B355" s="7">
-        <v>642</v>
+        <v>216</v>
       </c>
       <c t="s" r="C355" s="7">
         <v>14</v>
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="F355" s="7">
         <v>321</v>
@@ -12758,13 +12767,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H355" s="8">
-        <v>100</v>
+        <v>282</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>196</v>
+        <v>262</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
@@ -12775,29 +12784,29 @@
         <v>13</v>
       </c>
       <c r="B356" s="7">
-        <v>643</v>
+        <v>217</v>
       </c>
       <c t="s" r="C356" s="7">
         <v>14</v>
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="F356" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G356" s="8">
-        <v>100</v>
+        <v>282</v>
       </c>
       <c t="s" r="H356" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>25</v>
+        <v>434</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>432</v>
+        <v>87</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -12830,7 +12839,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
@@ -12850,7 +12859,7 @@
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
       <c t="s" r="M358" s="7">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="359" ht="14.25" customHeight="1">
@@ -12865,7 +12874,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
@@ -12880,12 +12889,12 @@
         <v>146</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
       <c t="s" r="M359" s="7">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="360" ht="15" customHeight="1">
@@ -12900,7 +12909,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
@@ -12933,7 +12942,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
@@ -12945,7 +12954,7 @@
         <v>100</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>309</v>
+        <v>255</v>
       </c>
       <c t="s" r="J361" s="7">
         <v>195</v>
@@ -12966,7 +12975,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -12978,10 +12987,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>311</v>
+        <v>280</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
@@ -12999,7 +13008,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -13011,7 +13020,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c t="s" r="J363" s="7">
         <v>113</v>
@@ -13047,7 +13056,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="F365" s="7">
         <v>320</v>
@@ -13082,7 +13091,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="F366" s="7">
         <v>320</v>
@@ -13115,7 +13124,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="F367" s="7">
         <v>320</v>
@@ -13124,7 +13133,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H367" s="8">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c t="s" r="I367" s="7">
         <v>46</v>
@@ -13148,13 +13157,13 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="F368" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G368" s="8">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c t="s" r="H368" s="8">
         <v>30</v>
@@ -13196,22 +13205,22 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G370" s="8">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c t="s" r="H370" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c t="s" r="K370" s="7">
         <v>231</v>
@@ -13233,7 +13242,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F371" s="7">
         <v>321</v>
@@ -13248,7 +13257,7 @@
         <v>59</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c t="s" r="K371" s="7">
         <v>122</v>
@@ -13270,7 +13279,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
@@ -13307,7 +13316,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
@@ -13322,7 +13331,7 @@
         <v>157</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -13355,7 +13364,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
@@ -13364,7 +13373,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H375" s="8">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c t="s" r="I375" s="7">
         <v>119</v>
@@ -13390,13 +13399,13 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="F376" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G376" s="8">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c t="s" r="H376" s="8">
         <v>30</v>
@@ -13425,7 +13434,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
@@ -13440,7 +13449,7 @@
         <v>102</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -13458,7 +13467,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
@@ -13491,7 +13500,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="F379" s="7">
         <v>321</v>
@@ -13506,7 +13515,7 @@
         <v>206</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -13524,7 +13533,7 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="F380" s="7">
         <v>321</v>
@@ -13536,7 +13545,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c t="s" r="J380" s="7">
         <v>338</v>
@@ -13572,13 +13581,13 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="F382" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G382" s="8">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c t="s" r="H382" s="8">
         <v>89</v>
@@ -13587,7 +13596,7 @@
         <v>215</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c t="s" r="K382" s="7">
         <v>84</v>
@@ -13609,7 +13618,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="F383" s="7">
         <v>330</v>
@@ -13618,10 +13627,10 @@
         <v>89</v>
       </c>
       <c t="s" r="H383" s="8">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>449</v>
+        <v>355</v>
       </c>
       <c t="s" r="J383" s="7">
         <v>215</v>
@@ -13657,7 +13666,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F385" s="7">
         <v>330</v>
@@ -13669,7 +13678,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c t="s" r="J385" s="7">
         <v>143</v>
@@ -13692,7 +13701,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F386" s="7">
         <v>330</v>
@@ -13701,18 +13710,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H386" s="8">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c t="s" r="I386" s="7">
         <v>313</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
       <c t="s" r="M386" s="7">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="387" ht="14.25" customHeight="1">
@@ -13727,16 +13736,16 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F387" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G387" s="8">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c t="s" r="H387" s="8">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c t="s" r="I387" s="7">
         <v>148</v>
@@ -13760,19 +13769,19 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F388" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G388" s="8">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c t="s" r="H388" s="8">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c t="s" r="J388" s="7">
         <v>229</v>
@@ -13808,7 +13817,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F390" s="7">
         <v>330</v>
@@ -13817,7 +13826,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H390" s="8">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c t="s" r="I390" s="7">
         <v>75</v>
@@ -13843,13 +13852,13 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F391" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G391" s="8">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c t="s" r="H391" s="8">
         <v>30</v>
@@ -13858,7 +13867,7 @@
         <v>227</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
@@ -13891,7 +13900,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F393" s="7">
         <v>330</v>
@@ -13903,7 +13912,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c t="s" r="J393" s="7">
         <v>101</v>
@@ -13924,7 +13933,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F394" s="7">
         <v>330</v>
@@ -13957,7 +13966,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F395" s="7">
         <v>330</v>
@@ -13966,7 +13975,7 @@
         <v>89</v>
       </c>
       <c t="s" r="H395" s="8">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c t="s" r="I395" s="7">
         <v>128</v>
@@ -13987,32 +13996,32 @@
         <v>26</v>
       </c>
       <c t="s" r="B396" s="7">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c t="s" r="C396" s="7">
         <v>14</v>
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F396" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G396" s="8">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c t="s" r="H396" s="8">
         <v>89</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c t="s" r="J396" s="7">
         <v>98</v>
       </c>
       <c t="s" r="K396" s="7">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="L396" s="7"/>
       <c t="s" r="M396" s="7">
@@ -14046,7 +14055,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F398" s="7">
         <v>330</v>
@@ -14055,7 +14064,7 @@
         <v>89</v>
       </c>
       <c t="s" r="H398" s="8">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c t="s" r="I398" s="7">
         <v>143</v>
@@ -14064,7 +14073,7 @@
         <v>168</v>
       </c>
       <c t="s" r="K398" s="7">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="L398" s="7"/>
       <c t="s" r="M398" s="7">
@@ -14083,22 +14092,22 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F399" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G399" s="8">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c t="s" r="H399" s="8">
         <v>89</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
@@ -14131,7 +14140,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F401" s="7">
         <v>330</v>
@@ -14143,7 +14152,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c t="s" r="J401" s="7">
         <v>125</v>
@@ -14151,7 +14160,7 @@
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
       <c t="s" r="M401" s="7">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="402" ht="14.25" customHeight="1">
@@ -14166,7 +14175,7 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F402" s="7">
         <v>330</v>
@@ -14181,12 +14190,12 @@
         <v>164</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
       <c t="s" r="M402" s="7">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="403" ht="14.25" customHeight="1">
@@ -14201,7 +14210,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F403" s="7">
         <v>330</v>
@@ -14216,7 +14225,7 @@
         <v>20</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
@@ -14234,7 +14243,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F404" s="7">
         <v>330</v>
@@ -14267,7 +14276,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F405" s="7">
         <v>330</v>
@@ -14276,10 +14285,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H405" s="8">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c t="s" r="J405" s="7">
         <v>189</v>
@@ -14290,7 +14299,7 @@
     </row>
     <row r="406" ht="15.75" customHeight="1">
       <c t="s" r="A406" s="9">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B406" s="9"/>
       <c r="C406" s="9"/>
@@ -14310,7 +14319,7 @@
     <row r="407" ht="65.25" customHeight="1"/>
     <row r="408" ht="16.5" customHeight="1">
       <c t="s" r="A408" s="10">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B408" s="10"/>
       <c r="C408" s="10"/>
@@ -14323,7 +14332,7 @@
       <c r="J408" s="10"/>
       <c r="K408" s="10"/>
       <c t="s" r="L408" s="11">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M408" s="11"/>
       <c r="N408" s="11"/>
